--- a/tests/temp-all-tabs-test.xlsx
+++ b/tests/temp-all-tabs-test.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="668">
   <si>
     <t>L2-1.공정번호</t>
   </si>
@@ -251,7 +251,7 @@
     <t>Wafer TTV</t>
   </si>
   <si>
-    <t>CC</t>
+    <t>★</t>
   </si>
   <si>
     <t>정렬 정확도</t>
@@ -980,6 +980,9 @@
     <t>DC Power</t>
   </si>
   <si>
+    <t>◇</t>
+  </si>
+  <si>
     <t>전압 안정도</t>
   </si>
   <si>
@@ -1424,7 +1427,7 @@
     <t>L1-3.제품(반)요구사항</t>
   </si>
   <si>
-    <t>Au Bump 높이(Bump Height, μm) — CC</t>
+    <t>Au Bump 높이(Bump Height, μm) — ★</t>
   </si>
   <si>
     <t>Lot 식별 정확도(OCR ID Matching Accuracy)</t>
@@ -1475,13 +1478,13 @@
     <t>MES Interlock 작동 정확도(공정 Skip 방지)</t>
   </si>
   <si>
-    <t>Au Bump 전단강도(Shear Strength, gf) — CC</t>
-  </si>
-  <si>
-    <t>Au Bump 경도(Hardness, HV) — CC</t>
-  </si>
-  <si>
-    <t>Bump Co-planarity(μm) — CC</t>
+    <t>Au Bump 전단강도(Shear Strength, gf) — ★</t>
+  </si>
+  <si>
+    <t>Au Bump 경도(Hardness, HV) — ★</t>
+  </si>
+  <si>
+    <t>Bump Co-planarity(μm) — ★</t>
   </si>
   <si>
     <t>PKG TEST 수율(고객 요구 수율 이상)</t>
@@ -1499,7 +1502,7 @@
     <t>Au Seed 박막 두께(Au Seed Thickness, Å)</t>
   </si>
   <si>
-    <t>Au Bump 높이 균일도(Bump Co-planarity, μm) — CC</t>
+    <t>Au Bump 높이 균일도(Bump Co-planarity, μm) — ★</t>
   </si>
   <si>
     <t>Bump 높이 균일도(Plating Uniformity, %)</t>
@@ -1625,7 +1628,7 @@
     <t>Hardness 미달로 인한 Chip 기능 불량</t>
   </si>
   <si>
-    <t>Co-planarity CC 불량으로 인한 제품 조립 불가(고객 조립 Reject)</t>
+    <t>Co-planarity 불량으로 인한 제품 조립 불가(고객 조립 Reject)</t>
   </si>
   <si>
     <t>PKG TEST 수율 미달로 인한 고객 생산 Capa 손실</t>
@@ -2761,7 +2764,7 @@
         <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2772,7 +2775,7 @@
         <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2783,7 +2786,7 @@
         <v>134</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2794,7 +2797,7 @@
         <v>136</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2805,7 +2808,7 @@
         <v>138</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2816,7 +2819,7 @@
         <v>138</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2827,7 +2830,7 @@
         <v>132</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2838,7 +2841,7 @@
         <v>134</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2849,7 +2852,7 @@
         <v>136</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2860,7 +2863,7 @@
         <v>138</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2871,7 +2874,7 @@
         <v>132</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2882,7 +2885,7 @@
         <v>134</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2893,7 +2896,7 @@
         <v>136</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2904,7 +2907,7 @@
         <v>138</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2915,7 +2918,7 @@
         <v>132</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -2926,7 +2929,7 @@
         <v>134</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2937,7 +2940,7 @@
         <v>136</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2948,7 +2951,7 @@
         <v>138</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2959,7 +2962,7 @@
         <v>132</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2970,7 +2973,7 @@
         <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2981,7 +2984,7 @@
         <v>134</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2992,7 +2995,7 @@
         <v>136</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -3003,7 +3006,7 @@
         <v>138</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -3014,7 +3017,7 @@
         <v>132</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -3025,7 +3028,7 @@
         <v>134</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -3036,7 +3039,7 @@
         <v>136</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -3047,7 +3050,7 @@
         <v>138</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -3058,7 +3061,7 @@
         <v>132</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -3069,7 +3072,7 @@
         <v>134</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -3080,7 +3083,7 @@
         <v>136</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -3091,7 +3094,7 @@
         <v>138</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -3102,7 +3105,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -3113,7 +3116,7 @@
         <v>134</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -3124,7 +3127,7 @@
         <v>136</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -3135,7 +3138,7 @@
         <v>138</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -3146,7 +3149,7 @@
         <v>132</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -3157,7 +3160,7 @@
         <v>134</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -3168,7 +3171,7 @@
         <v>136</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -3179,7 +3182,7 @@
         <v>138</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -3190,7 +3193,7 @@
         <v>132</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -3201,7 +3204,7 @@
         <v>134</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -3212,7 +3215,7 @@
         <v>136</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -3223,7 +3226,7 @@
         <v>138</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -3234,7 +3237,7 @@
         <v>132</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -3245,7 +3248,7 @@
         <v>134</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -3256,7 +3259,7 @@
         <v>134</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -3267,7 +3270,7 @@
         <v>136</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -3278,7 +3281,7 @@
         <v>138</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -3289,7 +3292,7 @@
         <v>132</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -3300,7 +3303,7 @@
         <v>134</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -3311,7 +3314,7 @@
         <v>136</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -3322,7 +3325,7 @@
         <v>138</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -3333,7 +3336,7 @@
         <v>132</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -3344,7 +3347,7 @@
         <v>134</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -3355,7 +3358,7 @@
         <v>136</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -3366,7 +3369,7 @@
         <v>138</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -3377,7 +3380,7 @@
         <v>132</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3388,7 +3391,7 @@
         <v>134</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3399,7 +3402,7 @@
         <v>136</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3410,7 +3413,7 @@
         <v>138</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3421,7 +3424,7 @@
         <v>132</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3432,7 +3435,7 @@
         <v>134</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3443,7 +3446,7 @@
         <v>136</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3454,7 +3457,7 @@
         <v>138</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3465,7 +3468,7 @@
         <v>132</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3476,7 +3479,7 @@
         <v>134</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3487,7 +3490,7 @@
         <v>134</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3498,7 +3501,7 @@
         <v>136</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3509,7 +3512,7 @@
         <v>138</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3520,7 +3523,7 @@
         <v>132</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3531,7 +3534,7 @@
         <v>134</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3542,7 +3545,7 @@
         <v>136</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3553,7 +3556,7 @@
         <v>138</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3564,7 +3567,7 @@
         <v>132</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3575,7 +3578,7 @@
         <v>134</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3586,7 +3589,7 @@
         <v>136</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3597,7 +3600,7 @@
         <v>138</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3608,7 +3611,7 @@
         <v>132</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3619,7 +3622,7 @@
         <v>134</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3630,7 +3633,7 @@
         <v>136</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3641,7 +3644,7 @@
         <v>138</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3652,7 +3655,7 @@
         <v>132</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3663,7 +3666,7 @@
         <v>134</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3674,7 +3677,7 @@
         <v>136</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3685,7 +3688,7 @@
         <v>138</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3696,7 +3699,7 @@
         <v>132</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3707,7 +3710,7 @@
         <v>134</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3718,7 +3721,7 @@
         <v>136</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3729,7 +3732,7 @@
         <v>138</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -3763,7 +3766,7 @@
         <v>214</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -3777,7 +3780,7 @@
         <v>133</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3791,7 +3794,7 @@
         <v>135</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3805,7 +3808,7 @@
         <v>137</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3819,7 +3822,7 @@
         <v>139</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3833,7 +3836,7 @@
         <v>140</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3847,7 +3850,7 @@
         <v>141</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3861,7 +3864,7 @@
         <v>142</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3875,7 +3878,7 @@
         <v>143</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3889,7 +3892,7 @@
         <v>144</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3903,7 +3906,7 @@
         <v>145</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3917,7 +3920,7 @@
         <v>146</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3931,7 +3934,7 @@
         <v>147</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3945,7 +3948,7 @@
         <v>148</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3959,7 +3962,7 @@
         <v>149</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3973,7 +3976,7 @@
         <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3987,7 +3990,7 @@
         <v>151</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -4001,7 +4004,7 @@
         <v>152</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -4015,7 +4018,7 @@
         <v>153</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -4029,7 +4032,7 @@
         <v>154</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -4043,7 +4046,7 @@
         <v>155</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -4057,7 +4060,7 @@
         <v>156</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -4071,7 +4074,7 @@
         <v>158</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -4085,7 +4088,7 @@
         <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -4099,7 +4102,7 @@
         <v>150</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -4113,7 +4116,7 @@
         <v>151</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -4127,7 +4130,7 @@
         <v>160</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -4141,7 +4144,7 @@
         <v>161</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -4155,7 +4158,7 @@
         <v>162</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -4169,7 +4172,7 @@
         <v>163</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -4183,7 +4186,7 @@
         <v>164</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -4197,7 +4200,7 @@
         <v>165</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -4211,7 +4214,7 @@
         <v>166</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -4225,7 +4228,7 @@
         <v>167</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -4239,7 +4242,7 @@
         <v>168</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -4253,7 +4256,7 @@
         <v>169</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -4267,7 +4270,7 @@
         <v>170</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -4281,7 +4284,7 @@
         <v>171</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -4295,7 +4298,7 @@
         <v>172</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -4309,7 +4312,7 @@
         <v>173</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -4323,7 +4326,7 @@
         <v>174</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -4337,7 +4340,7 @@
         <v>175</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -4351,7 +4354,7 @@
         <v>176</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -4365,7 +4368,7 @@
         <v>177</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -4379,7 +4382,7 @@
         <v>178</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -4393,7 +4396,7 @@
         <v>179</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -4407,7 +4410,7 @@
         <v>180</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -4421,7 +4424,7 @@
         <v>181</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -4435,7 +4438,7 @@
         <v>182</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -4449,7 +4452,7 @@
         <v>183</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -4463,7 +4466,7 @@
         <v>184</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -4477,7 +4480,7 @@
         <v>185</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -4491,7 +4494,7 @@
         <v>186</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -4505,7 +4508,7 @@
         <v>187</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -4519,7 +4522,7 @@
         <v>188</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -4533,7 +4536,7 @@
         <v>189</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -4547,7 +4550,7 @@
         <v>190</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -4561,7 +4564,7 @@
         <v>191</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -4575,7 +4578,7 @@
         <v>192</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -4589,7 +4592,7 @@
         <v>193</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -4603,7 +4606,7 @@
         <v>194</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -4617,7 +4620,7 @@
         <v>195</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -4631,7 +4634,7 @@
         <v>196</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -4645,7 +4648,7 @@
         <v>197</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -4659,7 +4662,7 @@
         <v>141</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -4673,7 +4676,7 @@
         <v>198</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -4687,7 +4690,7 @@
         <v>199</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -4701,7 +4704,7 @@
         <v>200</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -4715,7 +4718,7 @@
         <v>144</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -4729,7 +4732,7 @@
         <v>201</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -4743,7 +4746,7 @@
         <v>202</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -4757,7 +4760,7 @@
         <v>151</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -4771,7 +4774,7 @@
         <v>203</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -4785,7 +4788,7 @@
         <v>204</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -4799,7 +4802,7 @@
         <v>150</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -4813,7 +4816,7 @@
         <v>151</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -4827,7 +4830,7 @@
         <v>205</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -4841,7 +4844,7 @@
         <v>206</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -4855,7 +4858,7 @@
         <v>146</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -4869,7 +4872,7 @@
         <v>147</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -4883,7 +4886,7 @@
         <v>207</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -4897,7 +4900,7 @@
         <v>208</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -4911,7 +4914,7 @@
         <v>198</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -4925,7 +4928,7 @@
         <v>200</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -4939,7 +4942,7 @@
         <v>209</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -4953,7 +4956,7 @@
         <v>210</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -4967,7 +4970,7 @@
         <v>211</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -4981,7 +4984,7 @@
         <v>212</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -4995,7 +4998,7 @@
         <v>213</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -5017,22 +5020,22 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -5055,98 +5058,98 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -5169,330 +5172,330 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -5515,402 +5518,402 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -5933,702 +5936,702 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -6656,25 +6659,25 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -7278,28 +7281,28 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -7322,10 +7325,10 @@
         <v>5</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -7348,10 +7351,10 @@
         <v>5</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -7374,10 +7377,10 @@
         <v>5</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -7400,10 +7403,10 @@
         <v>5</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -7426,10 +7429,10 @@
         <v>5</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -7452,10 +7455,10 @@
         <v>5</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -7478,10 +7481,10 @@
         <v>5</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -7504,10 +7507,10 @@
         <v>5</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -7530,10 +7533,10 @@
         <v>5</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -7556,10 +7559,10 @@
         <v>5</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -7582,10 +7585,10 @@
         <v>5</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -7608,10 +7611,10 @@
         <v>5</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -7634,10 +7637,10 @@
         <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -7660,10 +7663,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -7686,10 +7689,10 @@
         <v>5</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -7712,10 +7715,10 @@
         <v>5</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -7738,10 +7741,10 @@
         <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -7764,10 +7767,10 @@
         <v>5</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -7790,10 +7793,10 @@
         <v>5</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -7816,10 +7819,10 @@
         <v>5</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -7839,13 +7842,13 @@
         <v>315</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -7862,16 +7865,16 @@
         <v>235</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -7891,13 +7894,13 @@
         <v>315</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -7914,16 +7917,16 @@
         <v>235</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -7940,16 +7943,16 @@
         <v>236</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -7975,7 +7978,7 @@
         <v>5</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -7992,16 +7995,16 @@
         <v>236</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -8027,7 +8030,7 @@
         <v>5</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -8044,16 +8047,16 @@
         <v>238</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -8076,10 +8079,10 @@
         <v>5</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -8102,10 +8105,10 @@
         <v>5</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -8128,10 +8131,10 @@
         <v>5</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -8154,10 +8157,10 @@
         <v>5</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -8180,10 +8183,10 @@
         <v>5</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -8200,16 +8203,16 @@
         <v>243</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -8226,16 +8229,16 @@
         <v>244</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -8258,10 +8261,10 @@
         <v>5</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -8284,10 +8287,10 @@
         <v>5</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -8304,16 +8307,16 @@
         <v>247</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -8330,16 +8333,16 @@
         <v>248</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -8362,10 +8365,10 @@
         <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -8388,10 +8391,10 @@
         <v>5</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -8408,16 +8411,16 @@
         <v>251</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -8434,16 +8437,16 @@
         <v>252</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -8466,10 +8469,10 @@
         <v>5</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -8492,10 +8495,10 @@
         <v>5</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -8512,16 +8515,16 @@
         <v>255</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -8544,10 +8547,10 @@
         <v>5</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -8570,10 +8573,10 @@
         <v>5</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -8596,10 +8599,10 @@
         <v>5</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -8616,16 +8619,16 @@
         <v>259</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -8642,16 +8645,16 @@
         <v>260</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -8668,16 +8671,16 @@
         <v>259</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -8694,16 +8697,16 @@
         <v>260</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -8720,16 +8723,16 @@
         <v>261</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -8752,10 +8755,10 @@
         <v>5</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -8778,10 +8781,10 @@
         <v>5</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -8798,16 +8801,16 @@
         <v>264</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -8830,10 +8833,10 @@
         <v>5</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -8856,10 +8859,10 @@
         <v>5</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -8882,10 +8885,10 @@
         <v>5</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -8902,16 +8905,16 @@
         <v>268</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -8934,10 +8937,10 @@
         <v>5</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -8960,10 +8963,10 @@
         <v>5</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -8986,10 +8989,10 @@
         <v>5</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -9006,16 +9009,16 @@
         <v>272</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -9038,10 +9041,10 @@
         <v>5</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -9064,10 +9067,10 @@
         <v>5</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -9090,10 +9093,10 @@
         <v>5</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -9110,16 +9113,16 @@
         <v>276</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -9142,10 +9145,10 @@
         <v>5</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -9162,16 +9165,16 @@
         <v>278</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -9194,10 +9197,10 @@
         <v>5</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -9214,16 +9217,16 @@
         <v>280</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -9246,10 +9249,10 @@
         <v>5</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -9266,16 +9269,16 @@
         <v>280</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -9298,10 +9301,10 @@
         <v>5</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -9324,10 +9327,10 @@
         <v>5</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -9350,10 +9353,10 @@
         <v>5</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -9376,10 +9379,10 @@
         <v>5</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -9402,10 +9405,10 @@
         <v>5</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -9428,10 +9431,10 @@
         <v>5</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -9454,10 +9457,10 @@
         <v>5</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -9480,10 +9483,10 @@
         <v>5</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -9506,10 +9509,10 @@
         <v>5</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -9532,10 +9535,10 @@
         <v>5</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -9558,10 +9561,10 @@
         <v>5</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -9584,10 +9587,10 @@
         <v>5</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -9610,10 +9613,10 @@
         <v>5</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -9636,10 +9639,10 @@
         <v>5</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -9662,10 +9665,10 @@
         <v>5</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -9688,10 +9691,10 @@
         <v>5</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -9708,16 +9711,16 @@
         <v>295</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -9740,10 +9743,10 @@
         <v>5</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -9766,10 +9769,10 @@
         <v>5</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -9792,10 +9795,10 @@
         <v>5</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -9812,16 +9815,16 @@
         <v>299</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -9844,10 +9847,10 @@
         <v>5</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -9870,10 +9873,10 @@
         <v>5</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -9904,48 +9907,48 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>130</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -9960,30 +9963,30 @@
         <v>140</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>114</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
@@ -9998,30 +10001,30 @@
         <v>142</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>115</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
@@ -10034,30 +10037,30 @@
         <v>143</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>115</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -10072,30 +10075,30 @@
         <v>146</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>116</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
@@ -10110,22 +10113,22 @@
         <v>150</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>117</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -10148,30 +10151,30 @@
         <v>151</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>117</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>12</v>
@@ -10186,22 +10189,22 @@
         <v>154</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>118</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="L8" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -10224,28 +10227,28 @@
         <v>155</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>118</v>
       </c>
       <c r="J9" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="L9" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="7"/>
@@ -10256,30 +10259,30 @@
         <v>158</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>118</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="L10" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>12</v>
@@ -10294,22 +10297,22 @@
         <v>156</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>118</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -10332,30 +10335,30 @@
         <v>157</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>118</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>14</v>
@@ -10370,30 +10373,30 @@
         <v>150</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>117</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>16</v>
@@ -10408,22 +10411,22 @@
         <v>162</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>119</v>
       </c>
       <c r="J14" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="L14" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -10446,30 +10449,30 @@
         <v>163</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>119</v>
       </c>
       <c r="J15" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="K15" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="K15" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="L15" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>18</v>
@@ -10484,22 +10487,22 @@
         <v>166</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>120</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -10522,30 +10525,30 @@
         <v>167</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>120</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>20</v>
@@ -10560,22 +10563,22 @@
         <v>170</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>121</v>
       </c>
       <c r="J18" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="L18" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -10598,30 +10601,30 @@
         <v>171</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>121</v>
       </c>
       <c r="J19" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="K19" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="L19" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>22</v>
@@ -10636,30 +10639,30 @@
         <v>174</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>121</v>
       </c>
       <c r="J20" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="L20" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>24</v>
@@ -10674,22 +10677,22 @@
         <v>178</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>122</v>
       </c>
       <c r="J21" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="K21" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="L21" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -10712,30 +10715,30 @@
         <v>179</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>122</v>
       </c>
       <c r="J22" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="L22" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>24</v>
@@ -10750,30 +10753,30 @@
         <v>180</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>123</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>26</v>
@@ -10788,30 +10791,30 @@
         <v>183</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>121</v>
       </c>
       <c r="J24" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="L24" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>28</v>
@@ -10826,30 +10829,30 @@
         <v>187</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>124</v>
       </c>
       <c r="J25" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="K25" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="K25" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="L25" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>30</v>
@@ -10864,30 +10867,30 @@
         <v>191</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>124</v>
       </c>
       <c r="J26" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="L26" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>32</v>
@@ -10902,22 +10905,22 @@
         <v>195</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>125</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -10940,30 +10943,30 @@
         <v>197</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>125</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="L28" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>34</v>
@@ -10978,22 +10981,22 @@
         <v>198</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>126</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -11001,7 +11004,7 @@
         <v>5</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>5</v>
@@ -11016,30 +11019,30 @@
         <v>141</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>126</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>34</v>
@@ -11054,30 +11057,30 @@
         <v>199</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>127</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>36</v>
@@ -11092,30 +11095,30 @@
         <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>117</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>38</v>
@@ -11130,30 +11133,30 @@
         <v>150</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>117</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>40</v>
@@ -11168,30 +11171,30 @@
         <v>146</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>116</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>42</v>
@@ -11206,30 +11209,30 @@
         <v>198</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>128</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>44</v>
@@ -11244,22 +11247,22 @@
         <v>211</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -11502,93 +11505,93 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>130</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>3</v>
@@ -11621,40 +11624,40 @@
         <v>5</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>93</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T2" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>5</v>
@@ -11662,13 +11665,13 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>6</v>
@@ -11701,31 +11704,31 @@
         <v>5</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>94</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="W3" s="5" t="s">
         <v>5</v>
@@ -11742,13 +11745,13 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -11781,37 +11784,37 @@
         <v>5</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>95</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>5</v>
@@ -11822,13 +11825,13 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>8</v>
@@ -11861,28 +11864,28 @@
         <v>5</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>96</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="V5" s="5" t="s">
         <v>5</v>
@@ -11902,13 +11905,13 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
@@ -11941,31 +11944,31 @@
         <v>5</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>97</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="W6" s="3" t="s">
         <v>5</v>
@@ -11982,13 +11985,13 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>10</v>
@@ -12021,31 +12024,31 @@
         <v>5</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>97</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="W7" s="5" t="s">
         <v>5</v>
@@ -12062,13 +12065,13 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>12</v>
@@ -12095,60 +12098,60 @@
         <v>235</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>98</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R8" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="T8" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z8" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>12</v>
@@ -12172,63 +12175,63 @@
         <v>155</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>98</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R9" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="S9" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="S9" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="T9" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="V9" s="5" t="s">
-        <v>641</v>
-      </c>
-      <c r="W9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="4" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>12</v>
@@ -12255,60 +12258,60 @@
         <v>238</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>98</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R10" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="S10" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="S10" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="T10" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>12</v>
@@ -12335,60 +12338,60 @@
         <v>237</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>5</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>99</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="T11" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="Y11" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="U11" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="V11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="W11" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="X11" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="Y11" s="4" t="s">
-        <v>616</v>
-      </c>
       <c r="Z11" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
@@ -12412,63 +12415,63 @@
         <v>157</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>99</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="T12" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="Y12" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>616</v>
-      </c>
       <c r="Z12" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>14</v>
@@ -12501,31 +12504,31 @@
         <v>5</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>97</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U13" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="W13" s="5" t="s">
         <v>5</v>
@@ -12542,13 +12545,13 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>16</v>
@@ -12575,60 +12578,60 @@
         <v>243</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>100</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R14" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="S14" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="S14" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="T14" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>16</v>
@@ -12655,60 +12658,60 @@
         <v>244</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>5</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>100</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R15" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="S15" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="S15" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="T15" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="U15" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="V15" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="W15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="U15" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="V15" s="5" t="s">
-        <v>641</v>
-      </c>
-      <c r="W15" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="X15" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y15" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z15" s="4" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
@@ -12735,37 +12738,37 @@
         <v>247</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>101</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="W16" s="3" t="s">
         <v>5</v>
@@ -12782,13 +12785,13 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>18</v>
@@ -12815,37 +12818,37 @@
         <v>248</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>5</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O17" s="5" t="s">
         <v>101</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U17" s="5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="V17" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="W17" s="5" t="s">
         <v>5</v>
@@ -12862,13 +12865,13 @@
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>20</v>
@@ -12895,60 +12898,60 @@
         <v>251</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>102</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R18" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="S18" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="S18" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="T18" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>20</v>
@@ -12975,60 +12978,60 @@
         <v>252</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>5</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>102</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R19" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="S19" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="S19" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="T19" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="U19" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="V19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="W19" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="X19" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="Y19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z19" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="U19" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="V19" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="W19" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="X19" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="Y19" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z19" s="4" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>22</v>
@@ -13055,60 +13058,60 @@
         <v>255</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>103</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R20" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="S20" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="S20" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="T20" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>24</v>
@@ -13135,34 +13138,34 @@
         <v>260</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>5</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O21" s="5" t="s">
         <v>104</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R21" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="S21" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="S21" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="T21" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="U21" s="5" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="V21" s="5" t="s">
         <v>5</v>
@@ -13177,18 +13180,18 @@
         <v>5</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>24</v>
@@ -13212,63 +13215,63 @@
         <v>179</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>104</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R22" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="S22" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="S22" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="T22" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>24</v>
@@ -13295,60 +13298,60 @@
         <v>261</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>5</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O23" s="5" t="s">
         <v>105</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="U23" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="V23" s="5" t="s">
         <v>5</v>
       </c>
       <c r="W23" s="5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X23" s="5" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>26</v>
@@ -13375,60 +13378,60 @@
         <v>264</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>103</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R24" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="S24" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="S24" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="T24" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>28</v>
@@ -13455,60 +13458,60 @@
         <v>268</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>5</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O25" s="5" t="s">
         <v>106</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R25" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="S25" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="S25" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="T25" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="U25" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="V25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="W25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="X25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z25" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="U25" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="V25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="W25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="X25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y25" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z25" s="4" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>30</v>
@@ -13535,60 +13538,60 @@
         <v>272</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>107</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R26" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="S26" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="S26" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="T26" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>32</v>
@@ -13615,34 +13618,34 @@
         <v>276</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O27" s="5" t="s">
         <v>108</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="T27" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="U27" s="5" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="V27" s="5" t="s">
         <v>5</v>
@@ -13654,21 +13657,21 @@
         <v>5</v>
       </c>
       <c r="Y27" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Z27" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>32</v>
@@ -13695,60 +13698,60 @@
         <v>278</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>108</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R28" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="S28" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="S28" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="T28" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="V28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z28" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="U28" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="V28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z28" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>34</v>
@@ -13781,31 +13784,31 @@
         <v>5</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O29" s="5" t="s">
         <v>109</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="U29" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="V29" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="W29" s="5" t="s">
         <v>5</v>
@@ -13822,13 +13825,13 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>34</v>
@@ -13852,7 +13855,7 @@
         <v>199</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>309</v>
@@ -13861,25 +13864,25 @@
         <v>5</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>110</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="U30" s="3" t="s">
         <v>127</v>
@@ -13902,13 +13905,13 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>34</v>
@@ -13941,31 +13944,31 @@
         <v>5</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O31" s="5" t="s">
         <v>109</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="U31" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="V31" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="W31" s="5" t="s">
         <v>5</v>
@@ -13982,13 +13985,13 @@
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>36</v>
@@ -14021,31 +14024,31 @@
         <v>5</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>97</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>5</v>
@@ -14062,13 +14065,13 @@
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>38</v>
@@ -14101,31 +14104,31 @@
         <v>5</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O33" s="5" t="s">
         <v>97</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U33" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="V33" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="W33" s="5" t="s">
         <v>5</v>
@@ -14142,13 +14145,13 @@
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>40</v>
@@ -14181,28 +14184,28 @@
         <v>5</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>96</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="V34" s="3" t="s">
         <v>5</v>
@@ -14222,13 +14225,13 @@
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>42</v>
@@ -14255,37 +14258,37 @@
         <v>295</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>5</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O35" s="5" t="s">
         <v>111</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S35" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T35" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U35" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="V35" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="W35" s="5" t="s">
         <v>5</v>
@@ -14302,13 +14305,13 @@
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>44</v>
@@ -14335,34 +14338,34 @@
         <v>299</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O36" s="3" t="s">
         <v>112</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="V36" s="3" t="s">
         <v>5</v>
@@ -17962,7 +17965,7 @@
         <v>315</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -17976,7 +17979,7 @@
         <v>154</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>5</v>
@@ -17993,7 +17996,7 @@
         <v>156</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -18010,7 +18013,7 @@
         <v>158</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>5</v>
@@ -18112,7 +18115,7 @@
         <v>162</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>5</v>
@@ -18129,7 +18132,7 @@
         <v>163</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>5</v>
@@ -18180,10 +18183,10 @@
         <v>166</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -18197,7 +18200,7 @@
         <v>167</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>5</v>
@@ -18248,7 +18251,7 @@
         <v>170</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>5</v>
@@ -18265,7 +18268,7 @@
         <v>171</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>5</v>
@@ -18316,7 +18319,7 @@
         <v>174</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>5</v>
@@ -18384,10 +18387,10 @@
         <v>178</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -18401,7 +18404,7 @@
         <v>178</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>5</v>
@@ -18418,7 +18421,7 @@
         <v>180</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>5</v>
@@ -18469,7 +18472,7 @@
         <v>183</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>5</v>
@@ -18537,7 +18540,7 @@
         <v>187</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>5</v>
@@ -18605,7 +18608,7 @@
         <v>191</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>5</v>
@@ -18673,10 +18676,10 @@
         <v>195</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>73</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -18707,7 +18710,7 @@
         <v>197</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>5</v>
@@ -18741,7 +18744,7 @@
         <v>198</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>5</v>
@@ -19030,7 +19033,7 @@
         <v>198</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>5</v>
@@ -19098,7 +19101,7 @@
         <v>211</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>5</v>
